--- a/data/washington/raw/WDOH_species_key.xlsx
+++ b/data/washington/raw/WDOH_species_key.xlsx
@@ -8,20 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/wc_biotoxin_depuration/data/washington/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9888629A-8C5B-084F-8B26-FA0A3E431730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE61D741-3CDA-6D4C-A6E3-166D155D3805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22940" yWindow="2620" windowWidth="28040" windowHeight="17440" xr2:uid="{12E24EC2-7736-FB44-969E-F3F0EC894FCC}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20200" xr2:uid="{12E24EC2-7736-FB44-969E-F3F0EC894FCC}"/>
   </bookViews>
   <sheets>
     <sheet name="WDOH_species_key" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">WDOH_species_key!$A$1:$C$47</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="103">
   <si>
     <t>comm_name</t>
   </si>
@@ -113,9 +116,6 @@
     <t>Kumamoto oyster</t>
   </si>
   <si>
-    <t>Crassostrea sikamea</t>
-  </si>
-  <si>
     <t>Limpet</t>
   </si>
   <si>
@@ -264,6 +264,75 @@
   </si>
   <si>
     <t>Magallana gigas</t>
+  </si>
+  <si>
+    <t>Perna canaliculus</t>
+  </si>
+  <si>
+    <t>Monoplex pilearis</t>
+  </si>
+  <si>
+    <t>This is from New Zealand</t>
+  </si>
+  <si>
+    <t>Modiolus modiolus</t>
+  </si>
+  <si>
+    <t>This is from the Atlantic</t>
+  </si>
+  <si>
+    <t>Tagelus californianus</t>
+  </si>
+  <si>
+    <t>Is this right? Other ones are from atlantic</t>
+  </si>
+  <si>
+    <t>Saccostrea glomerata</t>
+  </si>
+  <si>
+    <t>very unsure about this one</t>
+  </si>
+  <si>
+    <t>Chlamys rubida</t>
+  </si>
+  <si>
+    <t>Chlamys hastata</t>
+  </si>
+  <si>
+    <t>Spiny scallop since pink above? Or just Chlamys spp.?</t>
+  </si>
+  <si>
+    <t>Ostrea lurida?</t>
+  </si>
+  <si>
+    <t>Protothaca staminea?</t>
+  </si>
+  <si>
+    <t>Hinnites giganteus??</t>
+  </si>
+  <si>
+    <t>Limpet spp.</t>
+  </si>
+  <si>
+    <t>Chiton spp.</t>
+  </si>
+  <si>
+    <t>Burrowing shrimp spp.</t>
+  </si>
+  <si>
+    <t>Apostichopus californicus</t>
+  </si>
+  <si>
+    <t>Only sea cucumber in WA?</t>
+  </si>
+  <si>
+    <t>Neverita lewisii</t>
+  </si>
+  <si>
+    <t>????</t>
+  </si>
+  <si>
+    <t>Magallana sikamea</t>
   </si>
 </sst>
 </file>
@@ -1136,7 +1205,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1148,7 +1217,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -1156,10 +1225,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1167,7 +1236,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1190,13 +1259,16 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
+      <c r="B6" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1211,6 +1283,9 @@
       <c r="A9" t="s">
         <v>12</v>
       </c>
+      <c r="B9" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -1233,7 +1308,7 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1248,6 +1323,9 @@
       <c r="A14" t="s">
         <v>20</v>
       </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -1261,39 +1339,60 @@
       <c r="A16" t="s">
         <v>23</v>
       </c>
+      <c r="B16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>24</v>
       </c>
+      <c r="B17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>26</v>
       </c>
+      <c r="B19" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>27</v>
       </c>
+      <c r="B20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1301,186 +1400,233 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" t="s">
         <v>32</v>
       </c>
-      <c r="B24" t="s">
-        <v>33</v>
+      <c r="C24" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" t="s">
         <v>35</v>
-      </c>
-      <c r="B26" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="B27" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" t="s">
         <v>38</v>
       </c>
-      <c r="B28" t="s">
-        <v>39</v>
+      <c r="C28" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" t="s">
         <v>40</v>
-      </c>
-      <c r="B29" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" t="s">
         <v>42</v>
-      </c>
-      <c r="B30" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
         <v>46</v>
       </c>
-      <c r="B33" t="s">
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+      <c r="B34" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+      <c r="B35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
         <v>49</v>
       </c>
-      <c r="B35" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+      <c r="B36" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+      <c r="B38" t="s">
+        <v>90</v>
+      </c>
+      <c r="C38" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="B39" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
         <v>53</v>
       </c>
-      <c r="B39" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+      <c r="B40" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>54</v>
       </c>
-      <c r="B40" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+      <c r="B41" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
         <v>55</v>
       </c>
-      <c r="B41" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+      <c r="B42" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
         <v>56</v>
       </c>
-      <c r="B42" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+      <c r="B43" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
         <v>57</v>
       </c>
-      <c r="B43" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="B44" t="s">
         <v>58</v>
       </c>
-      <c r="B44" t="s">
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+      <c r="B45" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+      <c r="B46" t="s">
         <v>61</v>
       </c>
-      <c r="B46" t="s">
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+      <c r="B47" t="s">
         <v>63</v>
       </c>
-      <c r="B47" t="s">
-        <v>64</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C47" xr:uid="{E53B4107-2B59-7C49-AB73-A5F20980BEFA}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C47">
+      <sortCondition ref="A1:A47"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1492,12 +1638,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/data/washington/raw/WDOH_species_key.xlsx
+++ b/data/washington/raw/WDOH_species_key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/wc_biotoxin_depuration/data/washington/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE61D741-3CDA-6D4C-A6E3-166D155D3805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD45B404-0BB6-9845-9D2A-AE36CCA20BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20200" xr2:uid="{12E24EC2-7736-FB44-969E-F3F0EC894FCC}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="21640" windowHeight="20200" xr2:uid="{12E24EC2-7736-FB44-969E-F3F0EC894FCC}"/>
   </bookViews>
   <sheets>
     <sheet name="WDOH_species_key" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="108">
   <si>
     <t>comm_name</t>
   </si>
@@ -140,9 +140,6 @@
     <t>Olympia oyster</t>
   </si>
   <si>
-    <t>Ostrea conchaphila</t>
-  </si>
-  <si>
     <t>Other</t>
   </si>
   <si>
@@ -254,12 +251,6 @@
     <t>Saxidomus gigantea</t>
   </si>
   <si>
-    <t>Tresus capax or Tresus nuttallii</t>
-  </si>
-  <si>
-    <t>Tresus spp.</t>
-  </si>
-  <si>
     <t>Ruditapes philippinarum</t>
   </si>
   <si>
@@ -302,12 +293,6 @@
     <t>Spiny scallop since pink above? Or just Chlamys spp.?</t>
   </si>
   <si>
-    <t>Ostrea lurida?</t>
-  </si>
-  <si>
-    <t>Protothaca staminea?</t>
-  </si>
-  <si>
     <t>Hinnites giganteus??</t>
   </si>
   <si>
@@ -333,6 +318,36 @@
   </si>
   <si>
     <t>Magallana sikamea</t>
+  </si>
+  <si>
+    <t>Tresus capax</t>
+  </si>
+  <si>
+    <t>https://wdfw.wa.gov/species-habitats/species?species=clam&amp;category=All</t>
+  </si>
+  <si>
+    <t>From WDFW species list</t>
+  </si>
+  <si>
+    <t>Could sometimes be Tresus nuttallii? From WDFW species list</t>
+  </si>
+  <si>
+    <t>Ostrea lurida</t>
+  </si>
+  <si>
+    <t>Or is it Ostrea conchaphila? O. lurdia on WDFW species list</t>
+  </si>
+  <si>
+    <t>Green (S. droebachiensis) or red (M. franciscanus)?</t>
+  </si>
+  <si>
+    <t>Northern kelp crab on WDFW species list</t>
+  </si>
+  <si>
+    <t>Bent-nose-macoma clam on WDFW species list</t>
+  </si>
+  <si>
+    <t>Nuttal's cockle on WDFW species list</t>
   </si>
 </sst>
 </file>
@@ -482,7 +497,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -660,6 +675,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -823,9 +844,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1206,7 +1228,7 @@
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="68" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -1217,7 +1239,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -1225,10 +1247,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1236,15 +1258,18 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1260,15 +1285,18 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" t="s">
-        <v>75</v>
+      <c r="B7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1284,15 +1312,18 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1304,11 +1335,14 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B12" t="s">
-        <v>74</v>
+      <c r="B12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1324,15 +1358,18 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>22</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1340,10 +1377,10 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1351,18 +1388,18 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>76</v>
+      <c r="B18" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1370,10 +1407,10 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1381,18 +1418,21 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B21" t="s">
-        <v>71</v>
+      <c r="B21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1400,7 +1440,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1408,26 +1448,29 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C24" t="s">
-        <v>93</v>
+      <c r="C24" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="A25" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B25" t="s">
-        <v>78</v>
+      <c r="B25" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1443,7 +1486,7 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1451,123 +1494,132 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" t="s">
         <v>39</v>
-      </c>
-      <c r="B29" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" t="s">
         <v>41</v>
       </c>
-      <c r="B30" t="s">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" t="s">
-        <v>79</v>
+      <c r="B31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B32" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="B33" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B33" t="s">
-        <v>46</v>
+      <c r="C33" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B34" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C37" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>66</v>
+        <v>65</v>
+      </c>
+      <c r="C39" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B41" t="s">
         <v>35</v>
@@ -1575,31 +1627,34 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>55</v>
+      </c>
+      <c r="B43" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B43" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="B44" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B44" t="s">
-        <v>58</v>
+      <c r="C44" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B45" t="s">
         <v>35</v>
@@ -1607,18 +1662,18 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" t="s">
         <v>60</v>
-      </c>
-      <c r="B46" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" t="s">
         <v>62</v>
-      </c>
-      <c r="B47" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1628,22 +1683,28 @@
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7654897E-009C-0548-8049-D243ACABE53D}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
